--- a/temp.xlsx
+++ b/temp.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\home\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448808EA-21F2-4C6A-95E2-CD5D784E8A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5634823D-E50B-4113-AC08-CFA983771DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{663CC946-1763-4F88-8B47-4553E0835194}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{663CC946-1763-4F88-8B47-4553E0835194}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="工作表2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,15 +32,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
   <si>
     <t>Gamma 2.0</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -54,21 +52,6 @@
   </si>
   <si>
     <t>Gamma 2.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>加總</t>
-  </si>
-  <si>
-    <t>平均值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>計算加總</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>計數</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -111,6 +94,737 @@
         <charset val="136"/>
       </rPr>
       <t>誤差</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">驗證 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>vcgt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 是否負責實際 LUT 校正</t>
+    </r>
+  </si>
+  <si>
+    <t>工作項目</t>
+  </si>
+  <si>
+    <t>主要工作內容</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>確定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>vcgt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>格式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="1"/>
+      </rPr>
+      <t>，被替換仍能正常運作</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. 修改 / 移除 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>vcgt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，重新套用 ICC Profile，量測螢幕輸出
+2. 移除除了vcgt外的所有資料確定ICC依然能運作
+o. 修改前 Profile → 修改後 Profile → OS 套用 → 顯示器實際輸出</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>確定電腦資源多大的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>vcgt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>資料</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>確認其</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>vcgt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>二進位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">格式
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="3"/>
+      </rPr>
+      <t>設計修改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="3"/>
+      </rPr>
+      <t>vcgt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="3"/>
+      </rPr>
+      <t>的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="3"/>
+      </rPr>
+      <t>tool
+3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>設計實驗確定vcgt格式，例如將RGB中RLUT設0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">
+4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">提取vcgt資料，並重新寫回ICC確定依然能運作 </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>寫入更大筆的資料到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>vcgt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>查看</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">電腦是否能讀取不損毀
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>驗證寫入的資料是確實有作用而不是被</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>GPU OS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">自己刪減調
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>看是否有機會將硬體校正資料寫入vcgt內部</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArgyllCMS code research</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>找</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> ICC Profile </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>生成入口
+2. 找</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> vcgt </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>生成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> code
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>找其他</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> calibration Tag</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 先生成存色溫 ICC
+2. 生成含gamma ICC
+3. 將過去使用 ICC 的vcgt提出並寫入生成的ICC內部，驗證是否能正常校正</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>將元件拔除並建立自己的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ICC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>生成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> tool</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">研究 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ArgyllCMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="1"/>
+      </rPr>
+      <t>的校正流程與</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>code</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="1"/>
+      </rPr>
+      <t>設計查看</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ICC PROFILE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="1"/>
+      </rPr>
+      <t>資料的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>GUI</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>使用兩款軟體做參考</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>找出他查看</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ICC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">code
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>或是直接讓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>生成相關</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">code
+o. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="1"/>
+      </rPr>
+      <t>需要使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>C#</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="1"/>
+      </rPr>
+      <t>加入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>DICOM</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>256</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>階</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -119,10 +833,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0.0_);[Red]\(0.0\)"/>
+  <numFmts count="3">
+    <numFmt numFmtId="176" formatCode="0.0_);[Red]\(0.0\)"/>
+    <numFmt numFmtId="177" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
+    <numFmt numFmtId="179" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -151,6 +867,58 @@
       <family val="4"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -174,7 +942,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -187,7 +955,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -524,23 +1319,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFA71D18-79BC-4227-A1E4-01F903C0E9A9}">
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:M22"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="1"/>
-    <col min="2" max="2" width="11.90625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="12" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7265625" style="1"/>
-    <col min="7" max="7" width="70.1796875" style="1" customWidth="1"/>
-    <col min="8" max="9" width="8.7265625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.7265625" style="1"/>
+    <col min="5" max="5" width="11.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.77734375" style="1"/>
+    <col min="7" max="7" width="9.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.44140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.77734375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.77734375" style="1"/>
+    <col min="13" max="13" width="12.21875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="16.2">
       <c r="A1" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -555,7 +1355,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13">
       <c r="A2" s="1">
         <v>5400</v>
       </c>
@@ -572,7 +1372,7 @@
         <v>5168</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13">
       <c r="A3" s="1">
         <v>6500</v>
       </c>
@@ -589,7 +1389,7 @@
         <v>6544</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13">
       <c r="A4" s="1">
         <v>9300</v>
       </c>
@@ -606,21 +1406,38 @@
         <v>9048</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:13">
+      <c r="A9" s="11">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="16.2">
       <c r="A10" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+        <v>7</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="3">
         <v>1.8</v>
       </c>
@@ -634,8 +1451,21 @@
         <f>B11-C11</f>
         <v>48</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="H11" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="I11" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J11" s="3">
+        <v>5390</v>
+      </c>
+      <c r="K11" s="3">
+        <v>1.85</v>
+      </c>
+      <c r="M11" s="12"/>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="3"/>
       <c r="B12" s="3">
         <v>6500</v>
@@ -647,8 +1477,19 @@
         <f t="shared" ref="D12:D22" si="0">B12-C12</f>
         <v>81</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="H12" s="3"/>
+      <c r="I12" s="3">
+        <v>6500</v>
+      </c>
+      <c r="J12" s="3">
+        <v>6517</v>
+      </c>
+      <c r="K12" s="3">
+        <v>1.85</v>
+      </c>
+      <c r="M12" s="12"/>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="3"/>
       <c r="B13" s="3">
         <v>9300</v>
@@ -660,8 +1501,19 @@
         <f t="shared" si="0"/>
         <v>254</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="H13" s="3"/>
+      <c r="I13" s="3">
+        <v>9300</v>
+      </c>
+      <c r="J13" s="3">
+        <v>9137</v>
+      </c>
+      <c r="K13" s="3">
+        <v>1.85</v>
+      </c>
+      <c r="M13" s="12"/>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="4">
         <v>2</v>
       </c>
@@ -675,8 +1527,21 @@
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="H14" s="4">
+        <v>2</v>
+      </c>
+      <c r="I14" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J14" s="3">
+        <v>5504</v>
+      </c>
+      <c r="K14" s="13">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="M14" s="12"/>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="3"/>
       <c r="B15" s="3">
         <v>6500</v>
@@ -688,8 +1553,19 @@
         <f t="shared" si="0"/>
         <v>-45</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="H15" s="3"/>
+      <c r="I15" s="3">
+        <v>6500</v>
+      </c>
+      <c r="J15" s="3">
+        <v>6512</v>
+      </c>
+      <c r="K15" s="3">
+        <v>2.02</v>
+      </c>
+      <c r="M15" s="12"/>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="3"/>
       <c r="B16" s="3">
         <v>9300</v>
@@ -701,8 +1577,19 @@
         <f t="shared" si="0"/>
         <v>255</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="H16" s="3"/>
+      <c r="I16" s="3">
+        <v>9300</v>
+      </c>
+      <c r="J16" s="3">
+        <v>9094</v>
+      </c>
+      <c r="K16" s="3">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="M16" s="12"/>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="3">
         <v>2.2000000000000002</v>
       </c>
@@ -716,8 +1603,21 @@
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="H17" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="I17" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J17" s="3">
+        <v>5394</v>
+      </c>
+      <c r="K17" s="3">
+        <v>2.25</v>
+      </c>
+      <c r="M17" s="12"/>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="3"/>
       <c r="B18" s="3">
         <v>6500</v>
@@ -729,8 +1629,19 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="H18" s="3"/>
+      <c r="I18" s="3">
+        <v>6500</v>
+      </c>
+      <c r="J18" s="3">
+        <v>6514</v>
+      </c>
+      <c r="K18" s="3">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="M18" s="12"/>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="3"/>
       <c r="B19" s="3">
         <v>9300</v>
@@ -742,8 +1653,19 @@
         <f t="shared" si="0"/>
         <v>253</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="H19" s="3"/>
+      <c r="I19" s="3">
+        <v>9300</v>
+      </c>
+      <c r="J19" s="3">
+        <v>9106</v>
+      </c>
+      <c r="K19" s="3">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="M19" s="12"/>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="3">
         <v>2.6</v>
       </c>
@@ -757,8 +1679,21 @@
         <f t="shared" si="0"/>
         <v>-4</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="H20" s="3">
+        <v>2.6</v>
+      </c>
+      <c r="I20" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J20" s="3">
+        <v>5357</v>
+      </c>
+      <c r="K20" s="3">
+        <v>2.61</v>
+      </c>
+      <c r="M20" s="12"/>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="3"/>
       <c r="B21" s="3">
         <v>6500</v>
@@ -770,8 +1705,15 @@
         <f t="shared" si="0"/>
         <v>-44</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="H21" s="3"/>
+      <c r="I21" s="3">
+        <v>6500</v>
+      </c>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="M21" s="12"/>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="3"/>
       <c r="B22" s="3">
         <v>9300</v>
@@ -783,6 +1725,114 @@
         <f t="shared" si="0"/>
         <v>252</v>
       </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3">
+        <v>9300</v>
+      </c>
+      <c r="J22" s="3">
+        <v>9150</v>
+      </c>
+      <c r="K22" s="3">
+        <v>2.62</v>
+      </c>
+      <c r="M22" s="12"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AF191C9-686E-434D-A3E1-E2DA9F0AB3E4}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
+  <cols>
+    <col min="1" max="1" width="68.109375" customWidth="1"/>
+    <col min="2" max="2" width="77.5546875" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="48.6">
+      <c r="A2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="64.2">
+      <c r="A3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="48">
+      <c r="A4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="48">
+      <c r="A6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="48.6">
+      <c r="A7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="46.8">
+      <c r="A8" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1"/>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/temp.xlsx
+++ b/temp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\home\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5634823D-E50B-4113-AC08-CFA983771DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6276E9-B9A8-4672-83FA-E66F94558366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{663CC946-1763-4F88-8B47-4553E0835194}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{663CC946-1763-4F88-8B47-4553E0835194}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -86,19 +89,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>誤差</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">驗證 </t>
     </r>
     <r>
@@ -825,6 +815,19 @@
         <charset val="136"/>
       </rPr>
       <t>階</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>時間</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -836,7 +839,7 @@
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0.0_);[Red]\(0.0\)"/>
     <numFmt numFmtId="177" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
-    <numFmt numFmtId="179" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -942,7 +945,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -979,10 +982,13 @@
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1320,25 +1326,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFA71D18-79BC-4227-A1E4-01F903C0E9A9}">
   <dimension ref="A1:M22"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.90625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="1" customWidth="1"/>
     <col min="4" max="4" width="12" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.77734375" style="1"/>
-    <col min="7" max="7" width="9.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.44140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.77734375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.44140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.77734375" style="1"/>
-    <col min="13" max="13" width="12.21875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.77734375" style="1"/>
+    <col min="5" max="5" width="11.81640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.81640625" style="1"/>
+    <col min="7" max="7" width="9.36328125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.81640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.453125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.08984375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.81640625" style="1"/>
+    <col min="13" max="13" width="12.1796875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="16.2">
+    <row r="1" spans="1:13" ht="17">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -1410,8 +1416,11 @@
       <c r="A9" s="11">
         <v>46296</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="16.2">
+      <c r="G9" s="11">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="17">
       <c r="A10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1421,17 +1430,18 @@
       <c r="C10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>7</v>
+      <c r="D10" s="3"/>
+      <c r="G10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>25</v>
@@ -1447,21 +1457,21 @@
       <c r="C11" s="3">
         <v>5352</v>
       </c>
-      <c r="D11" s="3">
-        <f>B11-C11</f>
-        <v>48</v>
+      <c r="D11" s="3"/>
+      <c r="G11" s="3">
+        <v>1.8</v>
       </c>
       <c r="H11" s="3">
-        <v>1.8</v>
+        <v>5400</v>
       </c>
       <c r="I11" s="3">
-        <v>5400</v>
-      </c>
-      <c r="J11" s="3">
-        <v>5390</v>
-      </c>
-      <c r="K11" s="3">
-        <v>1.85</v>
+        <v>5346</v>
+      </c>
+      <c r="J11" s="14">
+        <v>1.82</v>
+      </c>
+      <c r="K11" s="13">
+        <v>0.48472222222222222</v>
       </c>
       <c r="M11" s="12"/>
     </row>
@@ -1473,19 +1483,19 @@
       <c r="C12" s="3">
         <v>6419</v>
       </c>
-      <c r="D12" s="3">
-        <f t="shared" ref="D12:D22" si="0">B12-C12</f>
-        <v>81</v>
-      </c>
-      <c r="H12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3">
+        <v>6500</v>
+      </c>
       <c r="I12" s="3">
-        <v>6500</v>
-      </c>
-      <c r="J12" s="3">
-        <v>6517</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1.85</v>
+        <v>6628</v>
+      </c>
+      <c r="J12" s="14">
+        <v>1.83</v>
+      </c>
+      <c r="K12" s="13">
+        <v>0.4381944444444445</v>
       </c>
       <c r="M12" s="12"/>
     </row>
@@ -1497,19 +1507,19 @@
       <c r="C13" s="3">
         <v>9046</v>
       </c>
-      <c r="D13" s="3">
-        <f t="shared" si="0"/>
-        <v>254</v>
-      </c>
-      <c r="H13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3">
+        <v>9300</v>
+      </c>
       <c r="I13" s="3">
-        <v>9300</v>
-      </c>
-      <c r="J13" s="3">
-        <v>9137</v>
-      </c>
-      <c r="K13" s="3">
-        <v>1.85</v>
+        <v>9090</v>
+      </c>
+      <c r="J13" s="14">
+        <v>1.82</v>
+      </c>
+      <c r="K13" s="13">
+        <v>0.45624999999999999</v>
       </c>
       <c r="M13" s="12"/>
     </row>
@@ -1523,21 +1533,21 @@
       <c r="C14" s="3">
         <v>5351</v>
       </c>
-      <c r="D14" s="3">
-        <f t="shared" si="0"/>
-        <v>49</v>
-      </c>
-      <c r="H14" s="4">
+      <c r="D14" s="3"/>
+      <c r="G14" s="4">
         <v>2</v>
       </c>
+      <c r="H14" s="3">
+        <v>5400</v>
+      </c>
       <c r="I14" s="3">
-        <v>5400</v>
-      </c>
-      <c r="J14" s="3">
-        <v>5504</v>
+        <v>5374</v>
+      </c>
+      <c r="J14" s="14">
+        <v>2</v>
       </c>
       <c r="K14" s="13">
-        <v>2.0299999999999998</v>
+        <v>0.43194444444444446</v>
       </c>
       <c r="M14" s="12"/>
     </row>
@@ -1549,19 +1559,19 @@
       <c r="C15" s="3">
         <v>6545</v>
       </c>
-      <c r="D15" s="3">
-        <f t="shared" si="0"/>
-        <v>-45</v>
-      </c>
-      <c r="H15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3">
+        <v>6500</v>
+      </c>
       <c r="I15" s="3">
-        <v>6500</v>
-      </c>
-      <c r="J15" s="3">
-        <v>6512</v>
-      </c>
-      <c r="K15" s="3">
-        <v>2.02</v>
+        <v>6587</v>
+      </c>
+      <c r="J15" s="14">
+        <v>2</v>
+      </c>
+      <c r="K15" s="13">
+        <v>0.50069444444444444</v>
       </c>
       <c r="M15" s="12"/>
     </row>
@@ -1573,19 +1583,19 @@
       <c r="C16" s="3">
         <v>9045</v>
       </c>
-      <c r="D16" s="3">
-        <f t="shared" si="0"/>
-        <v>255</v>
-      </c>
-      <c r="H16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3">
+        <v>9300</v>
+      </c>
       <c r="I16" s="3">
-        <v>9300</v>
-      </c>
-      <c r="J16" s="3">
         <v>9094</v>
       </c>
-      <c r="K16" s="3">
-        <v>2.0299999999999998</v>
+      <c r="J16" s="14">
+        <v>1.98</v>
+      </c>
+      <c r="K16" s="13">
+        <v>0.46319444444444446</v>
       </c>
       <c r="M16" s="12"/>
     </row>
@@ -1599,21 +1609,21 @@
       <c r="C17" s="3">
         <v>5314</v>
       </c>
-      <c r="D17" s="3">
-        <f t="shared" si="0"/>
-        <v>86</v>
+      <c r="D17" s="3"/>
+      <c r="G17" s="3">
+        <v>2.2000000000000002</v>
       </c>
       <c r="H17" s="3">
-        <v>2.2000000000000002</v>
+        <v>5400</v>
       </c>
       <c r="I17" s="3">
-        <v>5400</v>
-      </c>
-      <c r="J17" s="3">
-        <v>5394</v>
-      </c>
-      <c r="K17" s="3">
-        <v>2.25</v>
+        <v>5381</v>
+      </c>
+      <c r="J17" s="14">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="K17" s="13">
+        <v>0.52569444444444446</v>
       </c>
       <c r="M17" s="12"/>
     </row>
@@ -1625,19 +1635,19 @@
       <c r="C18" s="3">
         <v>6452</v>
       </c>
-      <c r="D18" s="3">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-      <c r="H18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3">
+        <v>6500</v>
+      </c>
       <c r="I18" s="3">
-        <v>6500</v>
-      </c>
-      <c r="J18" s="3">
-        <v>6514</v>
-      </c>
-      <c r="K18" s="3">
-        <v>2.2200000000000002</v>
+        <v>6472</v>
+      </c>
+      <c r="J18" s="14">
+        <v>2.19</v>
+      </c>
+      <c r="K18" s="13">
+        <v>0.45902777777777781</v>
       </c>
       <c r="M18" s="12"/>
     </row>
@@ -1649,19 +1659,19 @@
       <c r="C19" s="3">
         <v>9047</v>
       </c>
-      <c r="D19" s="3">
-        <f t="shared" si="0"/>
-        <v>253</v>
-      </c>
-      <c r="H19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3">
+        <v>9300</v>
+      </c>
       <c r="I19" s="3">
-        <v>9300</v>
-      </c>
-      <c r="J19" s="3">
-        <v>9106</v>
-      </c>
-      <c r="K19" s="3">
-        <v>2.2400000000000002</v>
+        <v>9103</v>
+      </c>
+      <c r="J19" s="14">
+        <v>2.19</v>
+      </c>
+      <c r="K19" s="13">
+        <v>0.46388888888888885</v>
       </c>
       <c r="M19" s="12"/>
     </row>
@@ -1675,21 +1685,21 @@
       <c r="C20" s="3">
         <v>5404</v>
       </c>
-      <c r="D20" s="3">
-        <f t="shared" si="0"/>
-        <v>-4</v>
+      <c r="D20" s="3"/>
+      <c r="G20" s="3">
+        <v>2.6</v>
       </c>
       <c r="H20" s="3">
-        <v>2.6</v>
+        <v>5400</v>
       </c>
       <c r="I20" s="3">
-        <v>5400</v>
-      </c>
-      <c r="J20" s="3">
-        <v>5357</v>
-      </c>
-      <c r="K20" s="3">
-        <v>2.61</v>
+        <v>5373</v>
+      </c>
+      <c r="J20" s="14">
+        <v>2.57</v>
+      </c>
+      <c r="K20" s="13">
+        <v>0.62986111111111109</v>
       </c>
       <c r="M20" s="12"/>
     </row>
@@ -1701,16 +1711,20 @@
       <c r="C21" s="3">
         <v>6544</v>
       </c>
-      <c r="D21" s="3">
-        <f t="shared" si="0"/>
-        <v>-44</v>
-      </c>
-      <c r="H21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3">
+        <v>6500</v>
+      </c>
       <c r="I21" s="3">
-        <v>6500</v>
-      </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
+        <v>6608</v>
+      </c>
+      <c r="J21" s="14">
+        <v>2.59</v>
+      </c>
+      <c r="K21" s="13">
+        <v>0.51597222222222217</v>
+      </c>
       <c r="M21" s="12"/>
     </row>
     <row r="22" spans="1:13">
@@ -1721,19 +1735,19 @@
       <c r="C22" s="3">
         <v>9048</v>
       </c>
-      <c r="D22" s="3">
-        <f t="shared" si="0"/>
-        <v>252</v>
-      </c>
-      <c r="H22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3">
+        <v>9300</v>
+      </c>
       <c r="I22" s="3">
-        <v>9300</v>
-      </c>
-      <c r="J22" s="3">
-        <v>9150</v>
-      </c>
-      <c r="K22" s="3">
-        <v>2.62</v>
+        <v>9103</v>
+      </c>
+      <c r="J22" s="14">
+        <v>2.61</v>
+      </c>
+      <c r="K22" s="13">
+        <v>0.5131944444444444</v>
       </c>
       <c r="M22" s="12"/>
     </row>
@@ -1747,80 +1761,80 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AF191C9-686E-434D-A3E1-E2DA9F0AB3E4}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="68.109375" customWidth="1"/>
-    <col min="2" max="2" width="77.5546875" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="68.08984375" customWidth="1"/>
+    <col min="2" max="2" width="77.54296875" customWidth="1"/>
+    <col min="6" max="6" width="8.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:2" ht="51">
+      <c r="A2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="66.5">
+      <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="48.6">
-      <c r="A2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="6" t="s">
+      <c r="B3" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="49.5">
+      <c r="A4" s="10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="64.2">
-      <c r="A3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="48">
-      <c r="A4" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="49.5">
+      <c r="A6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="48">
-      <c r="A6" s="3" t="s">
+    <row r="7" spans="1:2" ht="51">
+      <c r="A7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="48.6">
-      <c r="A7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="8" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="46.5">
+      <c r="A8" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="46.8">
-      <c r="A8" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1"/>
     </row>
@@ -1830,7 +1844,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" s="1"/>
     </row>

--- a/temp.xlsx
+++ b/temp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\home\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6276E9-B9A8-4672-83FA-E66F94558366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEB8509-DC2E-4B59-AB1B-AF71E5AF5C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{663CC946-1763-4F88-8B47-4553E0835194}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>Gamma 2.0</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1430,7 +1430,9 @@
       <c r="C10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3"/>
+      <c r="D10" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="G10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1457,7 +1459,9 @@
       <c r="C11" s="3">
         <v>5352</v>
       </c>
-      <c r="D11" s="3"/>
+      <c r="D11" s="3">
+        <v>1.83</v>
+      </c>
       <c r="G11" s="3">
         <v>1.8</v>
       </c>
@@ -1483,7 +1487,9 @@
       <c r="C12" s="3">
         <v>6419</v>
       </c>
-      <c r="D12" s="3"/>
+      <c r="D12" s="3">
+        <v>1.85</v>
+      </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3">
         <v>6500</v>
@@ -1507,7 +1513,9 @@
       <c r="C13" s="3">
         <v>9046</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="3">
+        <v>1.85</v>
+      </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3">
         <v>9300</v>
@@ -1533,7 +1541,9 @@
       <c r="C14" s="3">
         <v>5351</v>
       </c>
-      <c r="D14" s="3"/>
+      <c r="D14" s="3">
+        <v>2.0299999999999998</v>
+      </c>
       <c r="G14" s="4">
         <v>2</v>
       </c>
@@ -1559,7 +1569,9 @@
       <c r="C15" s="3">
         <v>6545</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="3">
+        <v>2.02</v>
+      </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3">
         <v>6500</v>
@@ -1583,7 +1595,9 @@
       <c r="C16" s="3">
         <v>9045</v>
       </c>
-      <c r="D16" s="3"/>
+      <c r="D16" s="3">
+        <v>2.0299999999999998</v>
+      </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3">
         <v>9300</v>
@@ -1609,7 +1623,9 @@
       <c r="C17" s="3">
         <v>5314</v>
       </c>
-      <c r="D17" s="3"/>
+      <c r="D17" s="3">
+        <v>2.2200000000000002</v>
+      </c>
       <c r="G17" s="3">
         <v>2.2000000000000002</v>
       </c>
@@ -1635,7 +1651,9 @@
       <c r="C18" s="3">
         <v>6452</v>
       </c>
-      <c r="D18" s="3"/>
+      <c r="D18" s="3">
+        <v>2.2200000000000002</v>
+      </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3">
         <v>6500</v>
@@ -1659,7 +1677,9 @@
       <c r="C19" s="3">
         <v>9047</v>
       </c>
-      <c r="D19" s="3"/>
+      <c r="D19" s="3">
+        <v>2.2400000000000002</v>
+      </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3">
         <v>9300</v>
@@ -1685,7 +1705,9 @@
       <c r="C20" s="3">
         <v>5404</v>
       </c>
-      <c r="D20" s="3"/>
+      <c r="D20" s="3">
+        <v>2.61</v>
+      </c>
       <c r="G20" s="3">
         <v>2.6</v>
       </c>
@@ -1711,7 +1733,9 @@
       <c r="C21" s="3">
         <v>6544</v>
       </c>
-      <c r="D21" s="3"/>
+      <c r="D21" s="3">
+        <v>2.6</v>
+      </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3">
         <v>6500</v>
@@ -1735,7 +1759,9 @@
       <c r="C22" s="3">
         <v>9048</v>
       </c>
-      <c r="D22" s="3"/>
+      <c r="D22" s="3">
+        <v>2.62</v>
+      </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3">
         <v>9300</v>
